--- a/Team-Data/2008-09/2-18-2008-09.xlsx
+++ b/Team-Data/2008-09/2-18-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593</v>
+        <v>0.585</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,40 +746,40 @@
         <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>7.7</v>
       </c>
       <c r="M2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P2" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.735</v>
+        <v>0.737</v>
       </c>
       <c r="R2" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V2" t="n">
         <v>12.9</v>
@@ -721,25 +788,25 @@
         <v>7.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>21</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -754,13 +821,13 @@
         <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -769,34 +836,34 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -811,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.796</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.387</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.776</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
@@ -903,37 +970,37 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -957,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -975,13 +1042,13 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -1025,94 +1092,94 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.407</v>
+        <v>0.396</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I4" t="n">
         <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M4" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N4" t="n">
         <v>0.364</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R4" t="n">
         <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
         <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1121,10 +1188,10 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1136,34 +1203,34 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT4" t="n">
         <v>26</v>
       </c>
-      <c r="AT4" t="n">
-        <v>25</v>
-      </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX4" t="n">
         <v>17</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,7 +1239,7 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -1222,37 +1289,37 @@
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
@@ -1267,25 +1334,25 @@
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y5" t="n">
         <v>5.6</v>
       </c>
-      <c r="Y5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1321,37 +1388,37 @@
         <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -1392,55 +1459,55 @@
         <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.804</v>
+        <v>0.784</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.475</v>
+        <v>0.472</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
         <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
         <v>12.9</v>
@@ -1449,34 +1516,34 @@
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1485,31 +1552,31 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM6" t="n">
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1524,22 +1591,22 @@
         <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,67 +1656,67 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
         <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
         <v>17.8</v>
       </c>
       <c r="P7" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
         <v>5.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA7" t="n">
         <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1679,10 +1746,10 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1691,16 +1758,16 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1721,7 +1788,7 @@
         <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1780,10 +1847,10 @@
         <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O8" t="n">
         <v>23</v>
@@ -1792,7 +1859,7 @@
         <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
         <v>10.3</v>
@@ -1804,13 +1871,13 @@
         <v>40.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>5.7</v>
@@ -1819,19 +1886,19 @@
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB8" t="n">
         <v>103.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1849,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
@@ -1882,7 +1949,7 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1900,13 +1967,13 @@
         <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2028,13 +2095,13 @@
         <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
         <v>27</v>
@@ -2043,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2058,10 +2125,10 @@
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2073,10 +2140,10 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
         <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O10" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P10" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
         <v>14.8</v>
@@ -2183,25 +2250,25 @@
         <v>5.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.7</v>
+        <v>107.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
@@ -2210,19 +2277,19 @@
         <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN10" t="n">
         <v>12</v>
@@ -2234,19 +2301,19 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2258,13 +2325,13 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2386,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
@@ -2401,7 +2468,7 @@
         <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2416,7 +2483,7 @@
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
         <v>17</v>
@@ -2437,10 +2504,10 @@
         <v>24</v>
       </c>
       <c r="AX11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2449,7 +2516,7 @@
         <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
@@ -2499,7 +2566,7 @@
         <v>38.8</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.452</v>
@@ -2511,55 +2578,55 @@
         <v>21.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
         <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
         <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X12" t="n">
         <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2568,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2589,31 +2656,31 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>22</v>
@@ -2622,13 +2689,13 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>0.236</v>
+        <v>0.241</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J13" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M13" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.751</v>
+        <v>0.754</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S13" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2726,31 +2793,31 @@
         <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
         <v>4</v>
@@ -2777,28 +2844,28 @@
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2813,7 +2880,7 @@
         <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -2860,43 +2927,43 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>85.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="P14" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2908,25 +2975,25 @@
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,19 +3011,19 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,13 +3053,13 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.278</v>
+        <v>0.283</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3045,7 +3112,7 @@
         <v>34.6</v>
       </c>
       <c r="J15" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K15" t="n">
         <v>0.449</v>
@@ -3057,19 +3124,19 @@
         <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S15" t="n">
         <v>28.7</v>
@@ -3081,7 +3148,7 @@
         <v>16.7</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.4</v>
@@ -3096,16 +3163,16 @@
         <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
@@ -3150,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
         <v>27</v>
@@ -3165,13 +3232,13 @@
         <v>12</v>
       </c>
       <c r="AX15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>21</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.528</v>
+        <v>0.538</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3230,7 +3297,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L16" t="n">
         <v>6.9</v>
@@ -3239,31 +3306,31 @@
         <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O16" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P16" t="n">
         <v>22.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="R16" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="U16" t="n">
         <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W16" t="n">
         <v>8.199999999999999</v>
@@ -3272,22 +3339,22 @@
         <v>5.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA16" t="n">
         <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3323,7 +3390,7 @@
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>27</v>
@@ -3332,13 +3399,13 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU16" t="n">
         <v>26</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>25</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3347,10 +3414,10 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>12</v>
@@ -3359,7 +3426,7 @@
         <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3409,61 +3476,61 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L17" t="n">
         <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
         <v>0.4</v>
@@ -3484,13 +3551,13 @@
         <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3502,16 +3569,16 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
         <v>21</v>
@@ -3520,19 +3587,19 @@
         <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>16</v>
       </c>
       <c r="AX17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,49 +3658,49 @@
         <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.335</v>
       </c>
       <c r="O18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P18" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q18" t="n">
         <v>0.772</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
         <v>6.4</v>
@@ -3645,19 +3712,19 @@
         <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3675,19 +3742,19 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -3699,13 +3766,13 @@
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
         <v>26</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.436</v>
+        <v>0.444</v>
       </c>
       <c r="H19" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I19" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
         <v>80.2</v>
@@ -3779,34 +3846,34 @@
         <v>0.443</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
         <v>20.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O19" t="n">
         <v>19.1</v>
       </c>
       <c r="P19" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
         <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U19" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V19" t="n">
         <v>13.4</v>
@@ -3815,31 +3882,31 @@
         <v>6.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB19" t="n">
         <v>98</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3848,7 +3915,7 @@
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
@@ -3857,19 +3924,19 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>8</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3878,10 +3945,10 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3893,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3908,7 +3975,7 @@
         <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.615</v>
+        <v>0.608</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J20" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O20" t="n">
         <v>18.7</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T20" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="U20" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,28 +4070,28 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA20" t="n">
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4033,10 +4100,10 @@
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>21</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>30</v>
@@ -4075,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4233,7 +4300,7 @@
         <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
@@ -4251,7 +4318,7 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>15</v>
@@ -4269,10 +4336,10 @@
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4415,7 +4482,7 @@
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
@@ -4433,13 +4500,13 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
         <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>22</v>
@@ -4448,7 +4515,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" t="n">
         <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>0.736</v>
+        <v>0.75</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J23" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.396</v>
@@ -4519,19 +4586,19 @@
         <v>19.8</v>
       </c>
       <c r="P23" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.718</v>
+        <v>0.722</v>
       </c>
       <c r="R23" t="n">
         <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
         <v>19.3</v>
@@ -4540,28 +4607,28 @@
         <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
         <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102</v>
+        <v>102.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,13 +4643,13 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4597,19 +4664,19 @@
         <v>11</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4618,7 +4685,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4627,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" t="n">
         <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.509</v>
+        <v>0.519</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.454</v>
+        <v>0.457</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
@@ -4698,10 +4765,10 @@
         <v>0.318</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P24" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0.745</v>
@@ -4713,10 +4780,10 @@
         <v>29.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U24" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V24" t="n">
         <v>15</v>
@@ -4731,40 +4798,40 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4788,19 +4855,19 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
         <v>16</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>17</v>
       </c>
       <c r="AV24" t="n">
         <v>20</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
@@ -4809,13 +4876,13 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39</v>
       </c>
       <c r="J25" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="L25" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
         <v>16.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
@@ -4886,46 +4953,46 @@
         <v>27.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U25" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="V25" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W25" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
         <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.8</v>
+        <v>105.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4940,10 +5007,10 @@
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4955,22 +5022,22 @@
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -4979,16 +5046,16 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
         <v>11</v>
@@ -4997,7 +5064,7 @@
         <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -5032,55 +5099,55 @@
         <v>52</v>
       </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.635</v>
+        <v>0.615</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P26" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
         <v>13.2</v>
@@ -5095,22 +5162,22 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>21.2</v>
       </c>
-      <c r="AA26" t="n">
-        <v>21.3</v>
-      </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5125,28 +5192,28 @@
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>19</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,19 +5222,19 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>21</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5176,13 +5243,13 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.204</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,37 +5296,37 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
         <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O27" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P27" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.803</v>
       </c>
       <c r="R27" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S27" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="T27" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
@@ -5271,25 +5338,25 @@
         <v>6.8</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z27" t="n">
         <v>23.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5322,10 +5389,10 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5340,10 +5407,10 @@
         <v>29</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>23</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5492,10 +5559,10 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>7</v>
@@ -5516,10 +5583,10 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
         <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M29" t="n">
         <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0.828</v>
       </c>
       <c r="R29" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V29" t="n">
         <v>13.2</v>
@@ -5635,28 +5702,28 @@
         <v>6.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.1</v>
+        <v>-2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5668,7 +5735,7 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
         <v>23</v>
@@ -5677,7 +5744,7 @@
         <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="n">
         <v>21</v>
@@ -5686,10 +5753,10 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,22 +5765,22 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
@@ -6017,25 +6084,25 @@
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6074,10 +6141,10 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY31" t="n">
         <v>18</v>
@@ -6089,7 +6156,7 @@
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-18-2008-09</t>
+          <t>2009-02-18</t>
         </is>
       </c>
     </row>
